--- a/artfynd/A 36377-2021 artfynd.xlsx
+++ b/artfynd/A 36377-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36377-2021 artfynd.xlsx
+++ b/artfynd/A 36377-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108953461</v>
+        <v>111742269</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Påterud, Vrm</t>
+          <t>Väst Eketjärn , Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>331865.3249102213</v>
+        <v>331780</v>
       </c>
       <c r="R2" t="n">
-        <v>6626546.724625999</v>
+        <v>6626525</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,33 +758,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Jeanette Fahlstad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Jeanette Fahlstad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111742269</v>
+        <v>111742278</v>
       </c>
       <c r="B3" t="n">
-        <v>94134</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,7 +816,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>331780</v>
+        <v>331819</v>
       </c>
       <c r="R3" t="n">
         <v>6626525</v>
@@ -894,48 +879,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111742281</v>
+        <v>111742294</v>
       </c>
       <c r="B4" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>331822</v>
+        <v>331800</v>
       </c>
       <c r="R4" t="n">
-        <v>6626518</v>
+        <v>6626511</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,12 +984,7 @@
         <v>111742299</v>
       </c>
       <c r="B5" t="n">
-        <v>94134</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111742294</v>
+        <v>111742256</v>
       </c>
       <c r="B6" t="n">
-        <v>94134</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,27 +1094,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>1049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1157,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>331800</v>
+        <v>331773</v>
       </c>
       <c r="R6" t="n">
-        <v>6626511</v>
+        <v>6626567</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,6 +1157,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-05-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På barklös talltorraka</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,43 +1189,43 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111742278</v>
+        <v>111742281</v>
       </c>
       <c r="B7" t="n">
-        <v>94134</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>100299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1264,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>331819</v>
+        <v>331822</v>
       </c>
       <c r="R7" t="n">
-        <v>6626525</v>
+        <v>6626518</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,6 +1293,210 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>111742319</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Väst Eketjärn , Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>331767</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6626481</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-05-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-05-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jeanette Fahlstad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jeanette Fahlstad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>108953461</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Påterud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>331866</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6626546</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-05-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-05-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
